--- a/results/02_taxa_assemblage/MRT_Method/ModelCompar/tables/confusion_matrix_all_refsites.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelCompar/tables/confusion_matrix_all_refsites.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Model A (fully trained on 35 core sites)</t>
+          <t>Model A (fully trained on 25 core sites)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -506,16 +506,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -525,35 +525,35 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Held-out (n=15)</t>
+          <t>Held-out (n=25)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>p_max=0.700</t>
+          <t>p_max=0.953</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dp=0.476</t>
+          <t>Dp=0.905</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -568,7 +568,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Model B (fully trained on 35 core + 10 peripheral sites)</t>
+          <t>Model B (fully trained on 25 core + 23 peripheral sites)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -621,16 +621,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
         <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -640,22 +640,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Held-out (n=5)</t>
+          <t>Held-out (n=2)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -663,12 +663,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>p_max=0.871</t>
+          <t>p_max=0.806</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dp=0.742</t>
+          <t>Dp=0.639</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -683,7 +683,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Model C (fully trained on 35 core + 10 peripheral sites, weighted)</t>
+          <t>Model C (fully trained on 25 core + 23 peripheral sites, weighted)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -698,13 +698,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -739,10 +739,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -770,20 +770,20 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Held-out (n=5)</t>
+          <t>Held-out (n=2)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>p_max=0.694</t>
+          <t>p_max=0.742</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Dp=0.448</t>
+          <t>Dp=0.483</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -798,7 +798,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Model D (fully trained on 35 core + 10 peripheral + 5 uncertain sites)</t>
+          <t>Model D (fully trained on 25 core + 23 peripheral + 2 uncertain sites)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -832,16 +832,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -851,16 +851,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="C26" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
         <v>3</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -870,16 +870,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C27" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">

--- a/results/02_taxa_assemblage/MRT_Method/ModelCompar/tables/confusion_matrix_all_refsites.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelCompar/tables/confusion_matrix_all_refsites.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Model A (fully trained on 25 core sites)</t>
+          <t>Model A (fully trained on 42 core sites)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -540,20 +540,20 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Held-out (n=25)</t>
+          <t>Held-out (n=8)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>p_max=0.953</t>
+          <t>p_max=0.595</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dp=0.905</t>
+          <t>Dp=0.381</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -568,7 +568,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Model B (fully trained on 25 core + 23 peripheral sites)</t>
+          <t>Model B (fully trained on 42 core + 6 peripheral sites)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -605,13 +605,13 @@
         <v>78</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -621,16 +621,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -640,16 +640,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -663,12 +663,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>p_max=0.806</t>
+          <t>p_max=0.744</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dp=0.639</t>
+          <t>Dp=0.538</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -683,7 +683,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Model C (fully trained on 25 core + 23 peripheral sites, weighted)</t>
+          <t>Model C (fully trained on 42 core + 6 peripheral sites, weighted)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -778,12 +778,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>p_max=0.742</t>
+          <t>p_max=0.664</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Dp=0.483</t>
+          <t>Dp=0.442</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -798,7 +798,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Model D (fully trained on 25 core + 23 peripheral + 2 uncertain sites)</t>
+          <t>Model D (fully trained on 42 core + 6 peripheral + 2 uncertain sites)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -851,16 +851,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -870,16 +870,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C27" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D27" t="n">
         <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
